--- a/public/uploads/media/default/sample_cash_invoices.xlsx
+++ b/public/uploads/media/default/sample_cash_invoices.xlsx
@@ -1,57 +1,62 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sahaf\Desktop\Mohamed\Sahafintech\new-ekstrabooks\public\uploads\media\default\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52F77867-4E0C-44B4-A6DC-CCC2106B3CB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
-    <sheet name="sample_cash_invoices" sheetId="1" r:id="rId1"/>
+    <sheet name="Worksheet" sheetId="1" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
-  <si>
-    <t>customer_name</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="33">
+  <si>
+    <t>invoice number</t>
+  </si>
+  <si>
+    <t>invoice date</t>
+  </si>
+  <si>
+    <t>customer name</t>
+  </si>
+  <si>
+    <t>project name</t>
   </si>
   <si>
     <t>title</t>
   </si>
   <si>
-    <t>order_number</t>
-  </si>
-  <si>
-    <t>invoice_date</t>
-  </si>
-  <si>
-    <t>transaction_currency</t>
-  </si>
-  <si>
-    <t>discount_type</t>
-  </si>
-  <si>
-    <t>discount_value</t>
+    <t>order number</t>
+  </si>
+  <si>
+    <t>transaction currency</t>
+  </si>
+  <si>
+    <t>exchange rate</t>
+  </si>
+  <si>
+    <t>discount type</t>
+  </si>
+  <si>
+    <t>discount value</t>
   </si>
   <si>
     <t>note</t>
   </si>
   <si>
-    <t>product_name</t>
+    <t>footer</t>
+  </si>
+  <si>
+    <t>product name</t>
+  </si>
+  <si>
+    <t>description</t>
   </si>
   <si>
     <t>quantity</t>
@@ -63,58 +68,91 @@
     <t>tax</t>
   </si>
   <si>
-    <t>debit_account</t>
-  </si>
-  <si>
-    <t>payment_method</t>
-  </si>
-  <si>
-    <t>Kelsey Phillips</t>
-  </si>
-  <si>
-    <t>LQP011</t>
+    <t>payment account</t>
+  </si>
+  <si>
+    <t>payment method</t>
+  </si>
+  <si>
+    <t>payment reference</t>
+  </si>
+  <si>
+    <t>CI-1001</t>
+  </si>
+  <si>
+    <t>3/26/2026</t>
+  </si>
+  <si>
+    <t>Existing Customer Name</t>
+  </si>
+  <si>
+    <t>Cash Invoice</t>
+  </si>
+  <si>
+    <t>ORD-1001</t>
   </si>
   <si>
     <t>USD</t>
   </si>
   <si>
-    <t>Product 3</t>
-  </si>
-  <si>
-    <t>GST</t>
-  </si>
-  <si>
-    <t>Bank Account</t>
-  </si>
-  <si>
-    <t>Bank Transfer</t>
-  </si>
-  <si>
-    <t>Cash Invoice</t>
-  </si>
-  <si>
-    <t>exchange_rate</t>
+    <t>Existing Product Name 1</t>
+  </si>
+  <si>
+    <t>Optional item description</t>
+  </si>
+  <si>
+    <t>VAT</t>
+  </si>
+  <si>
+    <t>Existing Cash or Bank Account</t>
+  </si>
+  <si>
+    <t>Existing Payment Method</t>
+  </si>
+  <si>
+    <t>REF-1001</t>
+  </si>
+  <si>
+    <t>Existing Product Name 2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
+      <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAF2FF"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -130,22 +168,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
 </styleSheet>
 </file>
 
@@ -160,44 +190,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -227,12 +257,12 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -271,259 +301,379 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:T3"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="14.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.36328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.54296875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.54296875" customWidth="1"/>
-    <col min="7" max="7" width="12.54296875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="4.6328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.1796875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.7265625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.453125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="4" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.6328125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.567" bestFit="true" customWidth="true" style="0"/>
+    <col min="2" max="2" width="15.282" bestFit="true" customWidth="true" style="0"/>
+    <col min="3" max="3" width="26.993" bestFit="true" customWidth="true" style="0"/>
+    <col min="4" max="4" width="15.282" bestFit="true" customWidth="true" style="0"/>
+    <col min="5" max="5" width="15.282" bestFit="true" customWidth="true" style="0"/>
+    <col min="6" max="6" width="15.282" bestFit="true" customWidth="true" style="0"/>
+    <col min="7" max="7" width="24.708" bestFit="true" customWidth="true" style="0"/>
+    <col min="8" max="8" width="16.425" bestFit="true" customWidth="true" style="0"/>
+    <col min="9" max="9" width="16.425" bestFit="true" customWidth="true" style="0"/>
+    <col min="10" max="10" width="17.567" bestFit="true" customWidth="true" style="0"/>
+    <col min="11" max="11" width="5.856" bestFit="true" customWidth="true" style="0"/>
+    <col min="12" max="12" width="8.141" bestFit="true" customWidth="true" style="0"/>
+    <col min="13" max="13" width="28.136" bestFit="true" customWidth="true" style="0"/>
+    <col min="14" max="14" width="30.564" bestFit="true" customWidth="true" style="0"/>
+    <col min="15" max="15" width="10.569" bestFit="true" customWidth="true" style="0"/>
+    <col min="16" max="16" width="11.711" bestFit="true" customWidth="true" style="0"/>
+    <col min="17" max="17" width="4.57" bestFit="true" customWidth="true" style="0"/>
+    <col min="18" max="18" width="35.277" bestFit="true" customWidth="true" style="0"/>
+    <col min="19" max="19" width="28.136" bestFit="true" customWidth="true" style="0"/>
+    <col min="20" max="20" width="21.138" bestFit="true" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+    <row r="1" spans="1:20">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="N1" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="O1" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" s="1">
-        <v>45374</v>
+        <v>22</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F2">
+        <v>23</v>
+      </c>
+      <c r="F2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2">
         <v>1</v>
       </c>
-      <c r="G2">
+      <c r="I2">
         <v>0</v>
       </c>
-      <c r="H2">
+      <c r="J2">
         <v>5</v>
       </c>
-      <c r="J2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K2">
+      <c r="M2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O2">
+        <v>2</v>
+      </c>
+      <c r="P2">
+        <v>150</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>28</v>
+      </c>
+      <c r="R2" t="s">
+        <v>29</v>
+      </c>
+      <c r="S2" t="s">
+        <v>30</v>
+      </c>
+      <c r="T2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20">
+      <c r="A3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3">
         <v>1</v>
       </c>
-      <c r="L2">
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>5</v>
+      </c>
+      <c r="M3" t="s">
+        <v>32</v>
+      </c>
+      <c r="N3" t="s">
         <v>27</v>
       </c>
-      <c r="M2" t="s">
-        <v>18</v>
-      </c>
-      <c r="N2" t="s">
-        <v>19</v>
-      </c>
-      <c r="O2" t="s">
-        <v>20</v>
+      <c r="O3">
+        <v>1</v>
+      </c>
+      <c r="P3">
+        <v>85</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>28</v>
+      </c>
+      <c r="R3" t="s">
+        <v>29</v>
+      </c>
+      <c r="S3" t="s">
+        <v>30</v>
+      </c>
+      <c r="T3" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
+  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
+  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
+    <oddHeader/>
+    <oddFooter/>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <tableParts count="0"/>
 </worksheet>
 </file>